--- a/backend/elderlycare-common/src/main/resources/excel_model/CheckInRegistration.xlsx
+++ b/backend/elderlycare-common/src/main/resources/excel_model/CheckInRegistration.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -461,7 +461,6 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,11 +499,6 @@
           <t>经办人</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -542,11 +536,6 @@
           <t>operator</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>operation</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -578,11 +567,6 @@
           <t>李管家</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>查看详情</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -614,11 +598,6 @@
           <t>李管家</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>查看详情</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -648,11 +627,6 @@
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>王护士</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>查看详情</t>
         </is>
       </c>
     </row>
